--- a/Algorithm/Acquisition/SignalCharacteristics/signalData.xlsx
+++ b/Algorithm/Acquisition/SignalCharacteristics/signalData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cranfield-my.sharepoint.com/personal/a_lavinorejas_261_cranfield_ac_uk/Documents/Documents/Group Design Project/Cranfield-LEO-PNT/Algorithm/Acquisition/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cranfield-my.sharepoint.com/personal/a_lavinorejas_261_cranfield_ac_uk/Documents/Documents/Group Design Project/Cranfield-LEO-PNT/Algorithm/Acquisition/SignalCharacteristics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{31AC4230-72C4-4582-8E31-DEF67DFFC137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{472921F9-5837-43F7-A322-0337B65D3855}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{31AC4230-72C4-4582-8E31-DEF67DFFC137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C251215-0BE3-45E3-A109-4D1766DBCABA}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="1100" windowWidth="19200" windowHeight="9980" xr2:uid="{C1A3185A-F3C0-4606-B2D6-D4D09FADDBA2}"/>
+    <workbookView xWindow="-27150" yWindow="12240" windowWidth="21600" windowHeight="10980" xr2:uid="{C1A3185A-F3C0-4606-B2D6-D4D09FADDBA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>ID</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>SymbolFreq</t>
+  </si>
+  <si>
+    <t>OW_BladeRF_20dBatt_6GB.bin</t>
   </si>
 </sst>
 </file>
@@ -446,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C04845A8-D2B3-4AA5-B1E2-4210EB6AE0BD}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -504,7 +507,7 @@
         <v>320000000</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D4" si="0">230400000</f>
+        <f t="shared" ref="D3:D5" si="0">230400000</f>
         <v>230400000</v>
       </c>
       <c r="E3" t="s">
@@ -523,6 +526,22 @@
         <v>360000000</v>
       </c>
       <c r="D4">
+        <f t="shared" si="0"/>
+        <v>230400000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <f>60000000</f>
+        <v>60000000</v>
+      </c>
+      <c r="D5">
         <f t="shared" si="0"/>
         <v>230400000</v>
       </c>

--- a/Algorithm/Acquisition/SignalCharacteristics/signalData.xlsx
+++ b/Algorithm/Acquisition/SignalCharacteristics/signalData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cranfield-my.sharepoint.com/personal/a_lavinorejas_261_cranfield_ac_uk/Documents/Documents/Group Design Project/Cranfield-LEO-PNT/Algorithm/Acquisition/SignalCharacteristics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{31AC4230-72C4-4582-8E31-DEF67DFFC137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C251215-0BE3-45E3-A109-4D1766DBCABA}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{31AC4230-72C4-4582-8E31-DEF67DFFC137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37EBFB50-868C-4B66-B742-44A8AA5E3B44}"/>
   <bookViews>
-    <workbookView xWindow="-27150" yWindow="12240" windowWidth="21600" windowHeight="10980" xr2:uid="{C1A3185A-F3C0-4606-B2D6-D4D09FADDBA2}"/>
+    <workbookView xWindow="747" yWindow="993" windowWidth="19200" windowHeight="9980" xr2:uid="{C1A3185A-F3C0-4606-B2D6-D4D09FADDBA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>ID</t>
   </si>
@@ -68,7 +68,13 @@
     <t>SymbolFreq</t>
   </si>
   <si>
-    <t>OW_BladeRF_20dBatt_6GB.bin</t>
+    <t>LNB_BladeRF_5s.bin</t>
+  </si>
+  <si>
+    <t>OW_BladeRF_6GB_real.bin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BladeRF generated signal, limitation on Sampling frequency </t>
   </si>
 </sst>
 </file>
@@ -449,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C04845A8-D2B3-4AA5-B1E2-4210EB6AE0BD}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -507,7 +513,7 @@
         <v>320000000</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D5" si="0">230400000</f>
+        <f t="shared" ref="D3:D6" si="0">230400000</f>
         <v>230400000</v>
       </c>
       <c r="E3" t="s">
@@ -535,13 +541,32 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <f>60000000</f>
         <v>60000000</v>
       </c>
       <c r="D5">
+        <f t="shared" si="0"/>
+        <v>230400000</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <f>60000000</f>
+        <v>60000000</v>
+      </c>
+      <c r="D6">
         <f t="shared" si="0"/>
         <v>230400000</v>
       </c>

--- a/Algorithm/Acquisition/SignalCharacteristics/signalData.xlsx
+++ b/Algorithm/Acquisition/SignalCharacteristics/signalData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cranfield-my.sharepoint.com/personal/a_lavinorejas_261_cranfield_ac_uk/Documents/Documents/Group Design Project/Cranfield-LEO-PNT/Algorithm/Acquisition/SignalCharacteristics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{31AC4230-72C4-4582-8E31-DEF67DFFC137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37EBFB50-868C-4B66-B742-44A8AA5E3B44}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="8_{31AC4230-72C4-4582-8E31-DEF67DFFC137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F63257B5-89F9-42F7-BA11-37765930E6EA}"/>
   <bookViews>
-    <workbookView xWindow="747" yWindow="993" windowWidth="19200" windowHeight="9980" xr2:uid="{C1A3185A-F3C0-4606-B2D6-D4D09FADDBA2}"/>
+    <workbookView xWindow="1833" yWindow="1833" windowWidth="19200" windowHeight="9980" xr2:uid="{C1A3185A-F3C0-4606-B2D6-D4D09FADDBA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>ID</t>
   </si>
@@ -59,9 +59,6 @@
     <t>Oscillator signal, should not have any Doppler</t>
   </si>
   <si>
-    <t>Signal captured, expect Doppler</t>
-  </si>
-  <si>
     <t>rx_stream-360.00-1975.00-1-10dB-11032026T110930.bin</t>
   </si>
   <si>
@@ -74,7 +71,28 @@
     <t>OW_BladeRF_6GB_real.bin</t>
   </si>
   <si>
-    <t xml:space="preserve">BladeRF generated signal, limitation on Sampling frequency </t>
+    <t>SG_bladerf_50MHz_-50dBm 1.bin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BladeRF received signal, limitation on Sampling frequency </t>
+  </si>
+  <si>
+    <t>SG_bladerf_50MHz_-70dBm.bin</t>
+  </si>
+  <si>
+    <t>Signal captured, expect Doppler, 2025/10/14 T 14:04:28:052939247</t>
+  </si>
+  <si>
+    <t>SG_bladerf_50db_50MHz.bin</t>
+  </si>
+  <si>
+    <t>SG_bladerf_50db_30MHz.bin</t>
+  </si>
+  <si>
+    <t>UT_BladeRF_short_noLNA_20dbatt.bin</t>
+  </si>
+  <si>
+    <t>UT_BladeRF_short_LNA_20db_att.bin</t>
   </si>
 </sst>
 </file>
@@ -136,6 +154,72 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>8468</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>15581</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>321736</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>132883</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB2CEE89-2E59-AEDA-0F05-5ACB49614C6E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9334501" y="379648"/>
+          <a:ext cx="4174068" cy="299335"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -455,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C04845A8-D2B3-4AA5-B1E2-4210EB6AE0BD}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -476,7 +560,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
@@ -513,11 +597,11 @@
         <v>320000000</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D6" si="0">230400000</f>
+        <f t="shared" ref="D3:D12" si="0">230400000</f>
         <v>230400000</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.5">
@@ -525,7 +609,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4">
         <f>360000000</f>
@@ -541,7 +625,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <f>60000000</f>
@@ -560,7 +644,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <f>60000000</f>
@@ -571,7 +655,104 @@
         <v>230400000</v>
       </c>
     </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <f>60000000</f>
+        <v>60000000</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>230400000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <f>60000000</f>
+        <v>60000000</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>230400000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <f>61440000</f>
+        <v>61440000</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>230400000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10">
+        <f>61440000</f>
+        <v>61440000</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>230400000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11">
+        <f>61440000</f>
+        <v>61440000</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>230400000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12">
+        <f>61440000</f>
+        <v>61440000</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>230400000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>